--- a/artfynd/A 38913-2023 artfynd.xlsx
+++ b/artfynd/A 38913-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118642356</v>
+        <v>118641985</v>
       </c>
       <c r="B2" t="n">
-        <v>103524</v>
+        <v>96810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223836</v>
+        <v>224363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig skogsbräsma</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa var. flexuosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>With.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsbo, 640 m NV, Ög</t>
+          <t>Långsbo, 560 m NV, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543347</v>
+        <v>543361</v>
       </c>
       <c r="R2" t="n">
-        <v>6450574</v>
+        <v>6450486</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -795,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118641985</v>
+        <v>118642356</v>
       </c>
       <c r="B3" t="n">
-        <v>96803</v>
+        <v>103531</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,34 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>223836</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig skogsbräsma</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Cardamine flexuosa var. flexuosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>With.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsbo, 560 m NV, Ög</t>
+          <t>Långsbo, 640 m NV, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543361</v>
+        <v>543347</v>
       </c>
       <c r="R3" t="n">
-        <v>6450486</v>
+        <v>6450574</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 38913-2023 artfynd.xlsx
+++ b/artfynd/A 38913-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118641985</v>
+        <v>118642356</v>
       </c>
       <c r="B2" t="n">
-        <v>96810</v>
+        <v>103531</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>223836</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig skogsbräsma</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Cardamine flexuosa var. flexuosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>With.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsbo, 560 m NV, Ög</t>
+          <t>Långsbo, 640 m NV, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543361</v>
+        <v>543347</v>
       </c>
       <c r="R2" t="n">
-        <v>6450486</v>
+        <v>6450574</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118642356</v>
+        <v>118641985</v>
       </c>
       <c r="B3" t="n">
-        <v>103531</v>
+        <v>96810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +811,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223836</v>
+        <v>224363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig skogsbräsma</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa var. flexuosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>With.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsbo, 640 m NV, Ög</t>
+          <t>Långsbo, 560 m NV, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543347</v>
+        <v>543361</v>
       </c>
       <c r="R3" t="n">
-        <v>6450574</v>
+        <v>6450486</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 38913-2023 artfynd.xlsx
+++ b/artfynd/A 38913-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,113 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130787139</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98895</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219793</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mossnycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza majalis subsp. sphagnicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Höppner) H. A. Pedersen &amp; Hedrén</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Slätgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>543414</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6450466</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1990-06-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1990-06-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Diabild finns.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vitmossgungfly vid göl.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38913-2023 artfynd.xlsx
+++ b/artfynd/A 38913-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130787139</v>
       </c>
       <c r="B4" t="n">
-        <v>98895</v>
+        <v>98908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38913-2023 artfynd.xlsx
+++ b/artfynd/A 38913-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130787139</v>
       </c>
       <c r="B4" t="n">
-        <v>98908</v>
+        <v>98909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38913-2023 artfynd.xlsx
+++ b/artfynd/A 38913-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130787139</v>
       </c>
       <c r="B4" t="n">
-        <v>98909</v>
+        <v>98912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38913-2023 artfynd.xlsx
+++ b/artfynd/A 38913-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130787139</v>
       </c>
       <c r="B4" t="n">
-        <v>98912</v>
+        <v>98926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38913-2023 artfynd.xlsx
+++ b/artfynd/A 38913-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>130787139</v>
       </c>
       <c r="B4" t="n">
-        <v>98926</v>
+        <v>98927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38913-2023 artfynd.xlsx
+++ b/artfynd/A 38913-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118642356</v>
+        <v>2474930</v>
       </c>
       <c r="B2" t="n">
-        <v>103536</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223836</v>
+        <v>219793</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig skogsbräsma</t>
+          <t>Mossnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa var. flexuosa</t>
+          <t>Dactylorhiza majalis subsp. sphagnicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>With.</t>
+          <t>(Höppner) H. A. Pedersen &amp; Hedrén</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsbo, 640 m NV, Ög</t>
+          <t>Slätgölen NV, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543347</v>
+        <v>543412</v>
       </c>
       <c r="R2" t="n">
-        <v>6450574</v>
+        <v>6450517</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>1978-07-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>1995-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,43 +754,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Surdråg i skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
+          <t>Stefan Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Projekt Östergötland Flora</t>
+          <t>Äldre fynd i Östergötlands flora x</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118641985</v>
+        <v>71633959</v>
       </c>
       <c r="B3" t="n">
-        <v>96815</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,37 +787,52 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>219793</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Mossnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>Dactylorhiza majalis subsp. sphagnicola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Höppner) H. A. Pedersen &amp; Hedrén</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsbo, 560 m NV, Ög</t>
+          <t>Slätgölen, 40 m VSV nordspetsen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543361</v>
+        <v>543418</v>
       </c>
       <c r="R3" t="n">
-        <v>6450486</v>
+        <v>6450520</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2018-05-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2018-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>smala ofläckade blad, i knopp. Återfynd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,38 +875,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Surdråg i skogsmark</t>
+          <t>gungflymosse i gölkant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Adam Bergner</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Projekt Östergötland Flora</t>
-        </is>
-      </c>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>130787139</v>
       </c>
       <c r="B4" t="n">
-        <v>98951</v>
+        <v>99056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,6 +1002,228 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118642356</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104805</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223836</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig skogsbräsma</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cardamine flexuosa var. flexuosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långsbo, 640 m NV, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>543347</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6450574</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Surdråg i skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Adam Bergner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Adam Bergner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Projekt Östergötland Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118641985</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långsbo, 560 m NV, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>543361</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6450486</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Surdråg i skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Adam Bergner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Adam Bergner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Projekt Östergötland Flora</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38913-2023 artfynd.xlsx
+++ b/artfynd/A 38913-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Äldre fynd i Östergötlands flora x</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2474930</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71633959</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130787139</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Projekt Östergötland Flora</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118642356</t>
         </is>
       </c>
     </row>
@@ -1224,8 +1249,20 @@
           <t>Projekt Östergötland Flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118641985</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>